--- a/data/trans_bre/IP1008-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP1008-Clase-trans_bre.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 0,52</t>
+          <t>-4,09; 0,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -719,12 +719,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,56</t>
+          <t>0,0; 5,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 3,58</t>
+          <t>-1,19; 3,79</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -794,7 +794,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 0,0</t>
+          <t>-2,78; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -874,17 +874,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,49</t>
+          <t>0,0; 2,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 1,34</t>
+          <t>-0,58; 1,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 2,3</t>
+          <t>-0,21; 2,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -954,17 +954,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 1,34</t>
+          <t>-2,17; 1,38</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 1,85</t>
+          <t>-1,97; 1,42</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,41</t>
+          <t>0,0; 3,94</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1039,12 +1039,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 0,0</t>
+          <t>-6,95; 0,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 3,83</t>
+          <t>-2,73; 3,11</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 0,41</t>
+          <t>-0,62; 0,54</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 0,76</t>
+          <t>-0,54; 0,72</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,04; 1,4</t>
+          <t>0,02; 1,42</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-90,66; 251,1</t>
+          <t>-85,54; 511,72</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-76,55; 445,8</t>
+          <t>-84,11; 388,84</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-31,95; 1354,51</t>
+          <t>-23,56; 1603,54</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP1008-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP1008-Clase-trans_bre.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 0,81</t>
+          <t>-4,15; 0,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -719,12 +719,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,55</t>
+          <t>0,0; 5,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 3,79</t>
+          <t>-1,3; 3,38</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -794,7 +794,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 0,0</t>
+          <t>-3,4; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -874,17 +874,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,41</t>
+          <t>0,0; 2,11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 1,07</t>
+          <t>-0,57; 1,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 2,35</t>
+          <t>-0,25; 2,64</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -954,17 +954,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 1,38</t>
+          <t>-2,21; 1,34</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 1,42</t>
+          <t>-1,93; 1,69</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,94</t>
+          <t>0,0; 3,8</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1039,12 +1039,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-6,95; 0,0</t>
+          <t>-6,19; 0,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 3,11</t>
+          <t>-1,92; 3,93</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 0,54</t>
+          <t>-0,74; 0,49</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 0,72</t>
+          <t>-0,52; 0,66</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,02; 1,42</t>
+          <t>0,04; 1,4</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-85,54; 511,72</t>
+          <t>-88,24; 312,48</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-84,11; 388,84</t>
+          <t>-76,14; 307,62</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-23,56; 1603,54</t>
+          <t>-27,42; 1643,27</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP1008-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP1008-Clase-trans_bre.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 0,52</t>
+          <t>-4,14; 0,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -719,12 +719,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,36</t>
+          <t>0,0; 5,56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 3,38</t>
+          <t>-1,28; 3,58</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -794,7 +794,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 0,0</t>
+          <t>-3,39; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -874,17 +874,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,11</t>
+          <t>0,0; 2,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 1,35</t>
+          <t>-0,58; 1,34</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 2,64</t>
+          <t>-0,25; 2,3</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -954,17 +954,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 1,34</t>
+          <t>-2,5; 1,34</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 1,69</t>
+          <t>-1,96; 1,85</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,8</t>
+          <t>0,0; 4,41</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1039,12 +1039,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-6,19; 0,0</t>
+          <t>-5,51; 0,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 3,93</t>
+          <t>-1,89; 3,83</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1114,12 +1114,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 0,49</t>
+          <t>-0,78; 0,41</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 0,66</t>
+          <t>-0,51; 0,76</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1129,17 +1129,17 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-88,24; 312,48</t>
+          <t>-90,66; 251,1</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-76,14; 307,62</t>
+          <t>-76,55; 445,8</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-27,42; 1643,27</t>
+          <t>-31,95; 1354,51</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP1008-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP1008-Clase-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -594,239 +603,123 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-0,89</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-63,75%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
+      <c r="C4" s="5" t="n">
+        <v>-0.8876536752349083</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>-0.6374943377463853</v>
+      </c>
+      <c r="G4" s="6" t="inlineStr"/>
+      <c r="H4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-4,14; 0,52</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-4.141163821426587</v>
+      </c>
+      <c r="D5" s="5" t="inlineStr"/>
+      <c r="E5" s="5" t="inlineStr"/>
+      <c r="F5" s="6" t="inlineStr"/>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.5159610768195561</v>
+      </c>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="6" t="inlineStr"/>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Grupo III</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>1,56</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,74</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>115,71%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 5,56</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-1,28; 3,58</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>1.555412452472639</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.7443305218128701</v>
+      </c>
+      <c r="F7" s="6" t="inlineStr"/>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>1.157109855440411</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Grupo IV y V</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-0,68</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr"/>
+      <c r="D8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-1.276057337695825</v>
+      </c>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-3,39; 0,0</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr"/>
+      <c r="D9" s="5" t="n">
+        <v>5.561390476911017</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>3.58066702088791</v>
+      </c>
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Grupo VI</t>
+          <t>Grupo IV y V</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -834,239 +727,129 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>0,69</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>0,05</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0,87</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>18,22%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>312,49%</t>
-        </is>
-      </c>
+      <c r="C10" s="5" t="n">
+        <v>-0.6778591528032396</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G10" s="6" t="inlineStr"/>
+      <c r="H10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,49</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-0,58; 1,34</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-0,25; 2,3</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-3.392687317063674</v>
+      </c>
+      <c r="D11" s="5" t="inlineStr"/>
+      <c r="E11" s="5" t="inlineStr"/>
+      <c r="F11" s="6" t="inlineStr"/>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Grupo VII</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="5" t="inlineStr"/>
+      <c r="E12" s="5" t="inlineStr"/>
+      <c r="F12" s="6" t="inlineStr"/>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-0,46</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-0,04</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1,16</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-42,5%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-4,64%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-2,5; 1,34</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-1,96; 1,85</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 4,41</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+      <c r="C13" s="5" t="n">
+        <v>0.6869365324555519</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.05199299674996396</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.8712333910443579</v>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.1822022074495997</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>3.124873250094324</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>No ha trabajado</t>
-        </is>
-      </c>
+      <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>-1,73</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>0,07</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>7,79%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-0.5766014854813936</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-0.2482903170928594</v>
+      </c>
+      <c r="F14" s="6" t="inlineStr"/>
+      <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>-5,51; 0,0</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>-1,89; 3,83</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>2.486165225830668</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>1.344105237902778</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>2.302202942822864</v>
+      </c>
+      <c r="F15" s="6" t="inlineStr"/>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Grupo VII</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1074,34 +857,24 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>-0,1</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>0,06</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,65</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-19,84%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>13,32%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>238,14%</t>
+      <c r="C16" s="5" t="n">
+        <v>-0.4640338168551357</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-0.0443745217521576</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>1.159731989723421</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>-0.4249700243055138</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.04635665972899373</v>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
         </is>
       </c>
     </row>
@@ -1109,42 +882,190 @@
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-0,78; 0,41</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-0,51; 0,76</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>0,04; 1,4</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-90,66; 251,1</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-76,55; 445,8</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-31,95; 1354,51</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-2.502695056212699</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-1.959972984192968</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="6" t="inlineStr"/>
+      <c r="G17" s="6" t="inlineStr"/>
+      <c r="H17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>1.341991839103581</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>1.85246658020377</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>4.405833022268692</v>
+      </c>
+      <c r="F18" s="6" t="inlineStr"/>
+      <c r="G18" s="6" t="inlineStr"/>
+      <c r="H18" s="6" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>-1.73025383989065</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>0.07295958292222807</v>
+      </c>
+      <c r="F19" s="6" t="inlineStr"/>
+      <c r="G19" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>0.07785019432032739</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr"/>
+      <c r="D20" s="5" t="n">
+        <v>-5.514194574018207</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>-1.885147287217998</v>
+      </c>
+      <c r="F20" s="6" t="inlineStr"/>
+      <c r="G20" s="6" t="inlineStr"/>
+      <c r="H20" s="6" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr"/>
+      <c r="D21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>3.833059147375424</v>
+      </c>
+      <c r="F21" s="6" t="inlineStr"/>
+      <c r="G21" s="6" t="inlineStr"/>
+      <c r="H21" s="6" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>-0.09915203107634185</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>0.06100735032563732</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>0.6538881727527741</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>-0.1983940825276519</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>0.1332387428385517</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>2.381444120998875</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-0.7757809855845912</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-0.5121405792007915</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>0.03620781959030737</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>-0.906621714337895</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>-0.7654717102071308</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>-0.3194706416347511</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>0.4067449052645821</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>0.7613030521871793</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>1.396554902493285</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>2.5109868381755</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>4.458015248199357</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>13.54511155206996</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1153,15 +1074,15 @@
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
